--- a/Data/FlightPlan/FPL_03OCT26.xlsx
+++ b/Data/FlightPlan/FPL_03OCT26.xlsx
@@ -416,6 +416,9 @@
     <t>05:30</t>
   </si>
   <si>
+    <t>07:47</t>
+  </si>
+  <si>
     <t>10:00</t>
   </si>
   <si>
@@ -467,7 +470,7 @@
     <t>05:00</t>
   </si>
   <si>
-    <t>06:26</t>
+    <t>06:34</t>
   </si>
   <si>
     <t>07:20</t>
@@ -578,6 +581,12 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
     <t>BOM</t>
   </si>
   <si>
@@ -629,9 +638,6 @@
     <t>VN-A554</t>
   </si>
   <si>
-    <t>14:05</t>
-  </si>
-  <si>
     <t>16:15</t>
   </si>
   <si>
@@ -659,6 +665,9 @@
     <t>07:45</t>
   </si>
   <si>
+    <t>10:52</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -779,9 +788,6 @@
     <t>12:00</t>
   </si>
   <si>
-    <t>17:40</t>
-  </si>
-  <si>
     <t>22:05</t>
   </si>
   <si>
@@ -851,12 +857,15 @@
     <t>VN-A640</t>
   </si>
   <si>
-    <t>10:01</t>
+    <t>10:02</t>
   </si>
   <si>
     <t>VN-A641</t>
   </si>
   <si>
+    <t>07:37</t>
+  </si>
+  <si>
     <t>18:30</t>
   </si>
   <si>
@@ -905,6 +914,9 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>10:38</t>
+  </si>
+  <si>
     <t>12:35</t>
   </si>
   <si>
@@ -1013,6 +1025,9 @@
     <t>05:20</t>
   </si>
   <si>
+    <t>06:36</t>
+  </si>
+  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -1115,6 +1130,9 @@
     <t>VN-A683</t>
   </si>
   <si>
+    <t>06:51</t>
+  </si>
+  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1127,6 +1145,9 @@
     <t>05:40</t>
   </si>
   <si>
+    <t>07:06</t>
+  </si>
+  <si>
     <t>03:05</t>
   </si>
   <si>
@@ -1214,7 +1235,7 @@
     <t>Total Record(s): 363</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 03, 2026 05:01</t>
+    <t xml:space="preserve">Generated on  Oct 03, 2026 05:54</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3677,7 +3698,9 @@
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
+      <c t="s" r="M70" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c t="s" r="A71" s="6">
@@ -3706,7 +3729,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3739,7 +3762,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3769,7 +3792,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>75</v>
@@ -3835,10 +3858,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3868,10 +3891,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3901,10 +3924,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3937,7 +3960,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3949,10 +3972,10 @@
         <v>126</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3970,7 +3993,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3982,7 +4005,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>52</v>
@@ -4003,7 +4026,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4018,7 +4041,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4036,7 +4059,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4048,10 +4071,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4084,7 +4107,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4096,15 +4119,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4119,7 +4142,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4131,7 +4154,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>22</v>
@@ -4152,7 +4175,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4164,10 +4187,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4185,7 +4208,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4197,7 +4220,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>73</v>
@@ -4218,7 +4241,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4230,7 +4253,7 @@
         <v>126</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>108</v>
@@ -4251,7 +4274,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4284,7 +4307,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4296,10 +4319,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4317,7 +4340,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4329,7 +4352,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>113</v>
@@ -4365,22 +4388,22 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4398,7 +4421,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4407,13 +4430,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="I94" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4431,13 +4454,13 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>41</v>
@@ -4446,7 +4469,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4464,7 +4487,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4476,10 +4499,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4512,7 +4535,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4521,13 +4544,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4545,19 +4568,19 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>55</v>
@@ -4578,7 +4601,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4587,13 +4610,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I100" s="7">
         <v>65</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4611,13 +4634,13 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H101" s="8">
         <v>30</v>
@@ -4626,7 +4649,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4644,7 +4667,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4656,7 +4679,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>96</v>
@@ -4692,7 +4715,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4704,10 +4727,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4725,7 +4748,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4758,7 +4781,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4770,7 +4793,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>76</v>
@@ -4791,7 +4814,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4806,7 +4829,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4824,7 +4847,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4839,7 +4862,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4872,13 +4895,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>41</v>
@@ -4887,7 +4910,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4905,7 +4928,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4920,7 +4943,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4938,7 +4961,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4950,10 +4973,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4986,7 +5009,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5001,11 +5024,15 @@
         <v>22</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>188</v>
-      </c>
-      <c r="K114" s="7"/>
+        <v>189</v>
+      </c>
+      <c t="s" r="K114" s="7">
+        <v>155</v>
+      </c>
       <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
+      <c t="s" r="M114" s="7">
+        <v>190</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c t="s" r="A115" s="6">
@@ -5019,7 +5046,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5036,9 +5063,13 @@
       <c t="s" r="J115" s="7">
         <v>46</v>
       </c>
-      <c r="K115" s="7"/>
+      <c t="s" r="K115" s="7">
+        <v>55</v>
+      </c>
       <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
+      <c t="s" r="M115" s="7">
+        <v>191</v>
+      </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c t="s" r="A116" s="6">
@@ -5052,7 +5083,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5061,13 +5092,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5085,19 +5116,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>20</v>
@@ -5133,7 +5164,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5142,10 +5173,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>73</v>
@@ -5166,13 +5197,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>41</v>
@@ -5199,7 +5230,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5214,7 +5245,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5232,7 +5263,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5244,10 +5275,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5280,7 +5311,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5289,10 +5320,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>43</v>
@@ -5313,22 +5344,22 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5346,7 +5377,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5361,7 +5392,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5379,7 +5410,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5391,10 +5422,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5412,7 +5443,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5421,13 +5452,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5460,7 +5491,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5472,7 +5503,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>33</v>
@@ -5493,7 +5524,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5505,10 +5536,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5526,7 +5557,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5538,7 +5569,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>130</v>
@@ -5559,7 +5590,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5571,10 +5602,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5607,7 +5638,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5622,7 +5653,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5640,7 +5671,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5652,7 +5683,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>105</v>
@@ -5673,7 +5704,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5682,7 +5713,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>75</v>
@@ -5706,13 +5737,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>41</v>
@@ -5739,7 +5770,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5748,10 +5779,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>48</v>
@@ -5787,7 +5818,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5799,14 +5830,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
-      <c r="M141" s="7"/>
+      <c t="s" r="M141" s="7">
+        <v>218</v>
+      </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
       <c t="s" r="A142" s="6">
@@ -5820,7 +5853,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5829,10 +5862,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>87</v>
@@ -5853,22 +5886,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5886,7 +5919,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5898,10 +5931,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5919,7 +5952,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5931,10 +5964,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5967,7 +6000,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6000,7 +6033,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6012,10 +6045,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6033,7 +6066,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6045,7 +6078,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>46</v>
@@ -6066,7 +6099,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6078,7 +6111,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>120</v>
@@ -6099,7 +6132,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6111,10 +6144,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6132,7 +6165,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6141,13 +6174,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6180,7 +6213,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6192,17 +6225,17 @@
         <v>30</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="K154" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6217,7 +6250,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6226,13 +6259,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6265,7 +6298,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6280,10 +6313,10 @@
         <v>86</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
@@ -6302,7 +6335,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6335,7 +6368,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6347,10 +6380,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6368,7 +6401,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6380,10 +6413,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6416,7 +6449,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6428,10 +6461,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6449,7 +6482,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6458,13 +6491,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6482,22 +6515,22 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6515,7 +6548,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6524,13 +6557,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6548,22 +6581,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6596,7 +6629,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6605,13 +6638,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6629,19 +6662,19 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>103</v>
@@ -6662,7 +6695,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6671,7 +6704,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>104</v>
@@ -6695,22 +6728,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6728,7 +6761,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6740,7 +6773,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>130</v>
@@ -6761,7 +6794,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6773,10 +6806,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6809,7 +6842,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6818,10 +6851,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>118</v>
@@ -6842,22 +6875,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6875,7 +6908,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6887,10 +6920,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6923,7 +6956,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6935,10 +6968,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6956,7 +6989,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6965,13 +6998,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6989,13 +7022,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>41</v>
@@ -7004,7 +7037,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7022,7 +7055,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7031,10 +7064,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>112</v>
@@ -7055,22 +7088,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7103,7 +7136,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7112,10 +7145,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>31</v>
@@ -7136,22 +7169,22 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7169,7 +7202,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7202,7 +7235,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7235,7 +7268,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7268,7 +7301,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7301,7 +7334,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7316,7 +7349,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7334,7 +7367,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7382,22 +7415,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7415,7 +7448,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7424,13 +7457,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7448,22 +7481,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7481,7 +7514,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7493,10 +7526,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7529,7 +7562,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7538,13 +7571,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7562,19 +7595,19 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>73</v>
@@ -7595,7 +7628,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7607,7 +7640,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>87</v>
@@ -7628,7 +7661,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7640,7 +7673,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>58</v>
@@ -7661,7 +7694,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7676,7 +7709,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7709,7 +7742,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7721,7 +7754,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>39</v>
@@ -7729,7 +7762,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -7744,7 +7777,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7756,10 +7789,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7777,7 +7810,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7792,7 +7825,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7810,7 +7843,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7822,10 +7855,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7858,7 +7891,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7873,11 +7906,13 @@
         <v>134</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
-      <c r="M210" s="7"/>
+      <c t="s" r="M210" s="7">
+        <v>284</v>
+      </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
       <c t="s" r="A211" s="6">
@@ -7891,7 +7926,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7906,7 +7941,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7924,7 +7959,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7939,7 +7974,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7957,7 +7992,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7972,7 +8007,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7990,7 +8025,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8002,10 +8037,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8038,7 +8073,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8053,11 +8088,13 @@
         <v>82</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
-      <c r="M216" s="7"/>
+      <c t="s" r="M216" s="7">
+        <v>95</v>
+      </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
@@ -8071,7 +8108,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8104,7 +8141,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8116,7 +8153,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>33</v>
@@ -8137,7 +8174,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8152,7 +8189,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8170,7 +8207,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8203,7 +8240,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8212,13 +8249,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8236,13 +8273,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>30</v>
@@ -8251,7 +8288,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8284,7 +8321,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8296,10 +8333,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8319,7 +8356,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8328,10 +8365,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>73</v>
@@ -8352,13 +8389,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>41</v>
@@ -8385,7 +8422,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8397,10 +8434,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8418,7 +8455,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8427,13 +8464,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8451,22 +8488,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8499,7 +8536,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8514,11 +8551,13 @@
         <v>20</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
-      <c r="M231" s="7"/>
+      <c t="s" r="M231" s="7">
+        <v>301</v>
+      </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c t="s" r="A232" s="6">
@@ -8532,7 +8571,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8547,7 +8586,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8565,7 +8604,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8580,7 +8619,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8598,7 +8637,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8613,7 +8652,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8631,7 +8670,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8643,7 +8682,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>35</v>
@@ -8679,19 +8718,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>109</v>
@@ -8712,7 +8751,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8721,13 +8760,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8745,13 +8784,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>30</v>
@@ -8760,7 +8799,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8778,7 +8817,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8793,7 +8832,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8826,7 +8865,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8841,7 +8880,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8859,7 +8898,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8871,10 +8910,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8892,7 +8931,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8904,10 +8943,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8925,7 +8964,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8958,7 +8997,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8967,7 +9006,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I246" s="7">
         <v>108</v>
@@ -8991,22 +9030,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9039,7 +9078,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9051,10 +9090,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9072,7 +9111,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9105,7 +9144,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9138,7 +9177,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9150,7 +9189,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>66</v>
@@ -9171,7 +9210,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9183,10 +9222,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9204,7 +9243,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9216,10 +9255,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9237,7 +9276,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9252,7 +9291,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9285,7 +9324,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9300,7 +9339,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9318,7 +9357,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9327,13 +9366,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9351,22 +9390,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9384,7 +9423,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9396,10 +9435,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9417,7 +9456,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9426,13 +9465,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9450,22 +9489,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9498,7 +9537,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9507,10 +9546,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>70</v>
@@ -9531,19 +9570,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>72</v>
@@ -9564,7 +9603,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9576,10 +9615,10 @@
         <v>106</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9597,7 +9636,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -9609,10 +9648,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9630,7 +9669,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9639,13 +9678,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9663,13 +9702,13 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>30</v>
@@ -9678,7 +9717,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9711,7 +9750,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9723,10 +9762,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9744,7 +9783,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9756,10 +9795,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9777,7 +9816,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9786,13 +9825,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9810,13 +9849,13 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>30</v>
@@ -9843,7 +9882,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9858,7 +9897,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9876,7 +9915,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9891,7 +9930,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9909,7 +9948,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9924,7 +9963,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9957,7 +9996,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9966,13 +10005,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>72</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9990,22 +10029,22 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10023,7 +10062,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10032,13 +10071,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10056,22 +10095,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10104,7 +10143,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10116,7 +10155,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>54</v>
@@ -10137,7 +10176,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10152,7 +10191,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10170,7 +10209,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10185,7 +10224,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10203,7 +10242,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10215,7 +10254,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>99</v>
@@ -10236,7 +10275,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10245,10 +10284,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>72</v>
@@ -10284,7 +10323,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10296,14 +10335,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
-      <c r="M290" s="7"/>
+      <c t="s" r="M290" s="7">
+        <v>246</v>
+      </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
       <c t="s" r="A291" s="6">
@@ -10317,7 +10358,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10329,10 +10370,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10365,7 +10406,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10374,17 +10415,19 @@
         <v>30</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
-      <c r="M293" s="7"/>
+      <c t="s" r="M293" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
       <c t="s" r="A294" s="6">
@@ -10398,19 +10441,19 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>96</v>
@@ -10431,7 +10474,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10443,10 +10486,10 @@
         <v>106</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10464,7 +10507,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10479,7 +10522,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10497,7 +10540,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10506,13 +10549,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10530,19 +10573,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>76</v>
@@ -10563,7 +10606,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10572,13 +10615,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10596,22 +10639,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10644,7 +10687,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10659,7 +10702,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10677,7 +10720,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10710,7 +10753,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10725,7 +10768,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10743,7 +10786,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10752,13 +10795,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10776,13 +10819,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>30</v>
@@ -10791,7 +10834,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10824,7 +10867,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10833,10 +10876,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>22</v>
@@ -10857,22 +10900,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10890,7 +10933,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10902,7 +10945,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>44</v>
@@ -10923,7 +10966,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10938,7 +10981,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10971,7 +11014,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10986,7 +11029,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11004,7 +11047,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11016,10 +11059,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11037,7 +11080,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11052,7 +11095,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11070,7 +11113,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11082,10 +11125,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11118,7 +11161,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11127,13 +11170,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11151,13 +11194,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>41</v>
@@ -11166,7 +11209,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11184,7 +11227,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11193,13 +11236,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11217,19 +11260,19 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>99</v>
@@ -11250,7 +11293,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11259,13 +11302,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11283,13 +11326,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>41</v>
@@ -11298,7 +11341,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11331,7 +11374,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11346,7 +11389,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11364,7 +11407,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11376,7 +11419,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>105</v>
@@ -11397,7 +11440,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11409,10 +11452,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11430,7 +11473,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11442,10 +11485,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11463,7 +11506,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11478,7 +11521,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11496,7 +11539,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11508,10 +11551,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11544,7 +11587,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11559,7 +11602,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11577,7 +11620,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11589,7 +11632,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>45</v>
@@ -11610,7 +11653,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11622,7 +11665,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>25</v>
@@ -11658,7 +11701,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11667,17 +11710,21 @@
         <v>30</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>200</v>
-      </c>
-      <c r="K336" s="7"/>
+        <v>203</v>
+      </c>
+      <c t="s" r="K336" s="7">
+        <v>147</v>
+      </c>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>263</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
@@ -11691,13 +11738,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>30</v>
@@ -11724,7 +11771,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11733,13 +11780,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11757,22 +11804,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11790,7 +11837,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11799,10 +11846,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>79</v>
@@ -11823,19 +11870,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>67</v>
@@ -11871,7 +11918,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -11883,7 +11930,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>31</v>
@@ -11904,7 +11951,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -11916,10 +11963,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11937,7 +11984,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11949,7 +11996,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>104</v>
@@ -11970,7 +12017,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -11982,10 +12029,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12003,7 +12050,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12018,7 +12065,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12036,7 +12083,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12051,7 +12098,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12069,7 +12116,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12084,7 +12131,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12102,7 +12149,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12117,7 +12164,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12150,7 +12197,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12162,14 +12209,16 @@
         <v>94</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>19</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
+      <c t="s" r="M352" s="7">
+        <v>232</v>
+      </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c t="s" r="A353" s="6">
@@ -12183,7 +12232,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12195,10 +12244,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12216,7 +12265,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12225,7 +12274,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>64</v>
@@ -12249,13 +12298,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>41</v>
@@ -12264,7 +12313,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12282,7 +12331,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12291,7 +12340,7 @@
         <v>41</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>108</v>
@@ -12315,19 +12364,19 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>34</v>
@@ -12348,7 +12397,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12357,13 +12406,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="I358" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12381,22 +12430,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12429,7 +12478,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12438,10 +12487,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>55</v>
@@ -12462,22 +12511,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12495,7 +12544,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12528,7 +12577,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12540,10 +12589,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12561,7 +12610,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12573,10 +12622,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12609,7 +12658,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12621,10 +12670,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12642,7 +12691,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12654,10 +12703,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12675,7 +12724,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12684,13 +12733,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12708,22 +12757,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12756,7 +12805,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12765,7 +12814,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>82</v>
@@ -12775,7 +12824,9 @@
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
+      <c t="s" r="M372" s="7">
+        <v>373</v>
+      </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c t="s" r="A373" s="6">
@@ -12789,13 +12840,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>30</v>
@@ -12804,7 +12855,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12822,7 +12873,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12837,7 +12888,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12855,7 +12906,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12867,7 +12918,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>54</v>
@@ -12888,7 +12939,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12921,7 +12972,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -12930,13 +12981,13 @@
         <v>102</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12954,22 +13005,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12987,7 +13038,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12999,10 +13050,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13035,7 +13086,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13047,14 +13098,16 @@
         <v>50</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
-      <c r="M381" s="7"/>
+      <c t="s" r="M381" s="7">
+        <v>378</v>
+      </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
       <c t="s" r="A382" s="6">
@@ -13068,7 +13121,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13083,7 +13136,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13101,7 +13154,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13113,10 +13166,10 @@
         <v>106</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13134,7 +13187,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13167,7 +13220,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13179,10 +13232,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13200,7 +13253,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13212,10 +13265,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13233,7 +13286,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13242,10 +13295,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>132</v>
@@ -13266,22 +13319,22 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13314,7 +13367,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13326,14 +13379,18 @@
         <v>63</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>232</v>
-      </c>
-      <c r="K390" s="7"/>
+        <v>235</v>
+      </c>
+      <c t="s" r="K390" s="7">
+        <v>31</v>
+      </c>
       <c r="L390" s="7"/>
-      <c r="M390" s="7"/>
+      <c t="s" r="M390" s="7">
+        <v>339</v>
+      </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
       <c t="s" r="A391" s="6">
@@ -13347,7 +13404,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13362,7 +13419,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13380,7 +13437,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13392,10 +13449,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13413,7 +13470,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13425,7 +13482,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>122</v>
@@ -13461,7 +13518,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13473,7 +13530,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>45</v>
@@ -13494,7 +13551,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13506,10 +13563,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13527,7 +13584,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13536,13 +13593,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13560,22 +13617,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13608,7 +13665,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13617,13 +13674,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13641,13 +13698,13 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>30</v>
@@ -13656,7 +13713,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13674,7 +13731,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13686,10 +13743,10 @@
         <v>102</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13707,7 +13764,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13719,10 +13776,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13755,7 +13812,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13775,7 +13832,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -13790,7 +13847,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13805,7 +13862,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13823,7 +13880,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13835,10 +13892,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13856,7 +13913,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13868,7 +13925,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>82</v>
@@ -13904,7 +13961,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -13913,13 +13970,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13937,13 +13994,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>41</v>
@@ -13952,7 +14009,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13970,7 +14027,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -13985,7 +14042,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14003,7 +14060,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14018,7 +14075,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14051,7 +14108,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14063,10 +14120,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14084,7 +14141,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14093,13 +14150,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14117,13 +14174,13 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>17</v>
@@ -14132,7 +14189,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14165,27 +14222,27 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14200,7 +14257,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14233,7 +14290,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14242,13 +14299,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14277,11 +14334,11 @@
         <v>1615</v>
       </c>
       <c t="s" r="C423" s="7">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14293,10 +14350,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14314,7 +14371,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -14326,10 +14383,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14347,7 +14404,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -14359,10 +14416,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14395,7 +14452,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
@@ -14410,7 +14467,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14428,7 +14485,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
@@ -14461,7 +14518,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -14473,10 +14530,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14494,7 +14551,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14506,10 +14563,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14527,7 +14584,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
@@ -14539,10 +14596,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14575,7 +14632,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -14587,7 +14644,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>48</v>
@@ -14608,7 +14665,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -14617,13 +14674,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14641,22 +14698,22 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14689,7 +14746,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -14701,15 +14758,15 @@
         <v>94</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -14724,7 +14781,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -14733,13 +14790,13 @@
         <v>94</v>
       </c>
       <c t="s" r="H438" s="8">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c t="s" r="I438" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14757,22 +14814,22 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G439" s="8">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c t="s" r="H439" s="8">
         <v>94</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14805,7 +14862,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
@@ -14814,13 +14871,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14838,22 +14895,22 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14861,7 +14918,7 @@
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c t="s" r="A443" s="9">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B443" s="9"/>
       <c r="C443" s="9"/>
@@ -14881,7 +14938,7 @@
     <row r="444" ht="65.25" customHeight="1"/>
     <row r="445" ht="17.25" customHeight="1">
       <c t="s" r="A445" s="10">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B445" s="10"/>
       <c r="C445" s="10"/>
@@ -14894,7 +14951,7 @@
       <c r="J445" s="10"/>
       <c r="K445" s="10"/>
       <c t="s" r="L445" s="11">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="M445" s="11"/>
       <c r="N445" s="11"/>

--- a/Data/FlightPlan/FPL_03OCT26.xlsx
+++ b/Data/FlightPlan/FPL_03OCT26.xlsx
@@ -356,6 +356,9 @@
     <t>00:10</t>
   </si>
   <si>
+    <t>00:15</t>
+  </si>
+  <si>
     <t>VN-A524</t>
   </si>
   <si>
@@ -617,6 +620,9 @@
     <t>02:10</t>
   </si>
   <si>
+    <t>02:18</t>
+  </si>
+  <si>
     <t>03:00</t>
   </si>
   <si>
@@ -812,7 +818,7 @@
     <t>23:15</t>
   </si>
   <si>
-    <t>00:15</t>
+    <t>00:40</t>
   </si>
   <si>
     <t>VN-A552</t>
@@ -926,6 +932,9 @@
     <t>06:55</t>
   </si>
   <si>
+    <t>01:15</t>
+  </si>
+  <si>
     <t>VN-A580</t>
   </si>
   <si>
@@ -1058,6 +1067,9 @@
     <t>17:38</t>
   </si>
   <si>
+    <t>23:34</t>
+  </si>
+  <si>
     <t>VN-A634</t>
   </si>
   <si>
@@ -1136,6 +1148,9 @@
     <t>22:05</t>
   </si>
   <si>
+    <t>23:08</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1148,6 +1163,9 @@
     <t>18:59</t>
   </si>
   <si>
+    <t>23:01</t>
+  </si>
+  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -1295,9 +1313,6 @@
     <t>22:55</t>
   </si>
   <si>
-    <t>23:13</t>
-  </si>
-  <si>
     <t>VN-A650</t>
   </si>
   <si>
@@ -1442,7 +1457,7 @@
     <t>16:38</t>
   </si>
   <si>
-    <t>01:15</t>
+    <t>01:41</t>
   </si>
   <si>
     <t>02:20</t>
@@ -1544,6 +1559,9 @@
     <t>01:30</t>
   </si>
   <si>
+    <t>01:39</t>
+  </si>
+  <si>
     <t>02:30</t>
   </si>
   <si>
@@ -1586,6 +1604,9 @@
     <t>21:26</t>
   </si>
   <si>
+    <t>23:29</t>
+  </si>
+  <si>
     <t>VN-A677</t>
   </si>
   <si>
@@ -1793,7 +1814,7 @@
     <t>Total Record(s): 363</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 03, 2026 21:35</t>
+    <t xml:space="preserve">Generated on  Oct 03, 2026 22:34</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3433,7 +3454,9 @@
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
+      <c t="s" r="M41" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="6"/>
@@ -3462,7 +3485,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3474,10 +3497,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3497,7 +3520,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3512,12 +3535,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3532,7 +3555,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3544,15 +3567,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3567,7 +3590,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3579,15 +3602,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3602,7 +3625,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3614,15 +3637,15 @@
         <v>93</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3637,7 +3660,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3649,15 +3672,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3683,11 +3706,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C50" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3696,18 +3719,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c t="s" r="M50" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -3722,13 +3745,13 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>33</v>
@@ -3742,7 +3765,7 @@
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3757,7 +3780,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3766,18 +3789,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3792,13 +3815,13 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>33</v>
@@ -3807,12 +3830,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3842,7 +3865,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3851,18 +3874,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I55" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c t="s" r="M55" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -3877,13 +3900,13 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>33</v>
@@ -3892,12 +3915,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3912,7 +3935,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3921,18 +3944,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3947,27 +3970,27 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3982,7 +4005,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3991,18 +4014,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -4017,22 +4040,22 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -4065,7 +4088,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -4080,12 +4103,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -4100,7 +4123,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -4115,12 +4138,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -4135,7 +4158,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -4150,12 +4173,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -4170,7 +4193,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4185,12 +4208,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -4220,7 +4243,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4229,13 +4252,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -4255,13 +4278,13 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>33</v>
@@ -4275,7 +4298,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4290,7 +4313,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4299,18 +4322,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4325,13 +4348,13 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>33</v>
@@ -4340,12 +4363,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4360,7 +4383,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4372,15 +4395,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4395,7 +4418,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4410,12 +4433,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4430,7 +4453,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4450,7 +4473,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4465,7 +4488,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4477,10 +4500,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4513,7 +4536,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4522,18 +4545,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4548,13 +4571,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>33</v>
@@ -4563,12 +4586,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4583,7 +4606,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4595,15 +4618,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4618,7 +4641,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4630,7 +4653,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>94</v>
@@ -4638,7 +4661,7 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4653,7 +4676,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4668,14 +4691,14 @@
         <v>25</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="K80" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4690,7 +4713,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4705,14 +4728,14 @@
         <v>108</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="K81" s="7">
         <v>53</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4727,7 +4750,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4736,17 +4759,19 @@
         <v>33</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
+      <c t="s" r="M82" s="7">
+        <v>203</v>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c t="s" r="A83" s="6">
@@ -4760,22 +4785,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4808,7 +4833,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4817,18 +4842,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4843,19 +4868,19 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>61</v>
@@ -4863,7 +4888,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4878,7 +4903,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4890,15 +4915,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4913,7 +4938,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4925,15 +4950,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4963,7 +4988,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4975,15 +5000,15 @@
         <v>93</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4998,7 +5023,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -5007,10 +5032,10 @@
         <v>93</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>22</v>
@@ -5018,7 +5043,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -5033,27 +5058,27 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>93</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5068,7 +5093,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -5080,7 +5105,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>91</v>
@@ -5088,7 +5113,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5103,7 +5128,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5115,7 +5140,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>96</v>
@@ -5123,7 +5148,7 @@
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5138,7 +5163,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5147,18 +5172,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5173,27 +5198,27 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5223,27 +5248,27 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5258,7 +5283,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5267,13 +5292,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5293,22 +5318,22 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5328,7 +5353,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5337,10 +5362,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>56</v>
@@ -5376,7 +5401,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5385,18 +5410,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5411,19 +5436,19 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>65</v>
@@ -5431,7 +5456,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5446,7 +5471,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5455,18 +5480,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="I105" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5481,27 +5506,27 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5516,7 +5541,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5528,10 +5553,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5564,7 +5589,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5576,15 +5601,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5599,7 +5624,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5614,12 +5639,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5634,7 +5659,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5643,7 +5668,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>96</v>
@@ -5654,7 +5679,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5669,19 +5694,19 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>71</v>
@@ -5689,7 +5714,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5704,7 +5729,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5716,10 +5741,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5748,17 +5773,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C115" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>47</v>
@@ -5767,12 +5792,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5783,11 +5808,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C116" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5796,7 +5821,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I116" s="7">
         <v>52</v>
@@ -5807,7 +5832,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5822,22 +5847,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5870,7 +5895,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5885,14 +5910,14 @@
         <v>22</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="K119" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5907,7 +5932,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5944,7 +5969,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5953,18 +5978,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>76</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5979,19 +6004,19 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>20</v>
@@ -6027,7 +6052,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6036,10 +6061,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>91</v>
@@ -6047,7 +6072,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6062,13 +6087,13 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>47</v>
@@ -6082,7 +6107,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6097,7 +6122,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6106,18 +6131,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6132,13 +6157,13 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>47</v>
@@ -6147,7 +6172,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -6180,7 +6205,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6189,10 +6214,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>49</v>
@@ -6200,7 +6225,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6215,22 +6240,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -6250,7 +6275,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6259,18 +6284,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6285,26 +6310,28 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>114</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -6318,7 +6345,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6327,13 +6354,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6366,7 +6393,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6378,7 +6405,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>37</v>
@@ -6401,7 +6428,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6410,7 +6437,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I136" s="7">
         <v>94</v>
@@ -6421,7 +6448,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6436,13 +6463,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>47</v>
@@ -6456,7 +6483,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6471,7 +6498,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6483,15 +6510,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6521,7 +6548,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6536,12 +6563,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6556,7 +6583,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6568,15 +6595,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6591,7 +6618,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6600,10 +6627,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>83</v>
@@ -6611,7 +6638,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6626,27 +6653,27 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6676,7 +6703,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6688,15 +6715,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6711,7 +6738,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6720,18 +6747,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6746,27 +6773,27 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6781,7 +6808,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6793,15 +6820,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6816,7 +6843,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6828,14 +6855,18 @@
         <v>32</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>304</v>
-      </c>
-      <c r="K149" s="7"/>
+        <v>306</v>
+      </c>
+      <c t="s" r="K149" s="7">
+        <v>307</v>
+      </c>
       <c r="L149" s="7"/>
-      <c r="M149" s="7"/>
+      <c t="s" r="M149" s="7">
+        <v>56</v>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="6"/>
@@ -6864,7 +6895,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6879,7 +6910,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6899,7 +6930,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6911,15 +6942,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6934,7 +6965,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6946,7 +6977,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>53</v>
@@ -6954,7 +6985,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6969,7 +7000,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6984,12 +7015,12 @@
         <v>111</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7000,11 +7031,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7016,7 +7047,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>76</v>
@@ -7033,11 +7064,11 @@
         <v>7658</v>
       </c>
       <c t="s" r="C156" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7046,13 +7077,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -7085,7 +7116,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -7097,17 +7128,17 @@
         <v>33</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="K158" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7122,7 +7153,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7131,18 +7162,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7157,13 +7188,13 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>33</v>
@@ -7172,12 +7203,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7192,7 +7223,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7201,13 +7232,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7240,7 +7271,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7249,20 +7280,20 @@
         <v>32</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="K163" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7277,13 +7308,13 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>47</v>
@@ -7295,11 +7326,11 @@
         <v>81</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7314,7 +7345,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7326,15 +7357,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7349,7 +7380,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7361,15 +7392,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7399,7 +7430,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7411,15 +7442,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7434,7 +7465,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7443,18 +7474,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7469,27 +7500,27 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7504,7 +7535,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7513,18 +7544,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7539,22 +7570,22 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7587,7 +7618,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7596,18 +7627,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7622,27 +7653,27 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>93</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7657,7 +7688,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7666,18 +7697,18 @@
         <v>93</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7692,27 +7723,27 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7727,7 +7758,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7742,12 +7773,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7762,7 +7793,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7774,15 +7805,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7808,11 +7839,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C181" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7821,18 +7852,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7843,23 +7874,23 @@
         <v>8521</v>
       </c>
       <c t="s" r="C182" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>27</v>
@@ -7867,7 +7898,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7882,7 +7913,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7894,14 +7925,16 @@
         <v>33</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c r="A184" s="6"/>
@@ -7930,7 +7963,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7942,15 +7975,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7965,7 +7998,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7977,15 +8010,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8000,7 +8033,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8015,12 +8048,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8050,7 +8083,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8059,10 +8092,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>34</v>
@@ -8070,7 +8103,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8085,27 +8118,27 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8120,7 +8153,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8140,7 +8173,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8155,7 +8188,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8175,7 +8208,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8190,7 +8223,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8210,7 +8243,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8225,7 +8258,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8245,7 +8278,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8260,7 +8293,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8269,18 +8302,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8295,19 +8328,19 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>75</v>
@@ -8315,7 +8348,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8345,27 +8378,27 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8380,7 +8413,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8389,18 +8422,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8415,27 +8448,27 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8465,7 +8498,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8474,18 +8507,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8500,19 +8533,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>91</v>
@@ -8520,7 +8553,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8535,7 +8568,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8547,10 +8580,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8570,7 +8603,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8582,7 +8615,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>70</v>
@@ -8590,7 +8623,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8605,7 +8638,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8617,14 +8650,16 @@
         <v>47</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
-      <c r="M206" s="7"/>
+      <c t="s" r="M206" s="7">
+        <v>379</v>
+      </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c r="A207" s="6"/>
@@ -8653,7 +8688,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8665,7 +8700,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>45</v>
@@ -8673,7 +8708,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8688,7 +8723,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8700,15 +8735,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8723,7 +8758,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8738,12 +8773,12 @@
         <v>26</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8758,7 +8793,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8770,14 +8805,16 @@
         <v>33</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
-      <c r="M211" s="7"/>
+      <c t="s" r="M211" s="7">
+        <v>384</v>
+      </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
       <c r="A212" s="6"/>
@@ -8806,7 +8843,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8818,15 +8855,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8841,7 +8878,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8856,12 +8893,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8876,7 +8913,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8888,10 +8925,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8911,7 +8948,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8923,15 +8960,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8946,7 +8983,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8958,15 +8995,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8996,7 +9033,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9005,18 +9042,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9031,13 +9068,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>47</v>
@@ -9046,12 +9083,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9066,7 +9103,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9075,18 +9112,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I221" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9101,13 +9138,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>47</v>
@@ -9116,12 +9153,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9151,7 +9188,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9166,12 +9203,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9186,7 +9223,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9198,7 +9235,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>45</v>
@@ -9206,7 +9243,7 @@
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9221,7 +9258,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9233,7 +9270,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>37</v>
@@ -9256,7 +9293,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9265,13 +9302,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9291,19 +9328,19 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>97</v>
@@ -9326,7 +9363,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9338,15 +9375,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9376,7 +9413,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9388,10 +9425,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9411,7 +9448,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9420,10 +9457,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>91</v>
@@ -9431,7 +9468,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9446,13 +9483,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>47</v>
@@ -9466,7 +9503,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9481,7 +9518,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9493,15 +9530,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9516,7 +9553,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9528,10 +9565,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9549,7 +9586,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9561,10 +9598,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9597,7 +9634,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9606,18 +9643,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9632,27 +9669,27 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9667,27 +9704,27 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9702,13 +9739,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>33</v>
@@ -9717,7 +9754,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9737,7 +9774,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9749,7 +9786,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>40</v>
@@ -9757,7 +9794,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9787,22 +9824,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9822,7 +9859,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9831,18 +9868,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9857,13 +9894,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>33</v>
@@ -9872,12 +9909,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9892,7 +9929,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9907,7 +9944,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9940,7 +9977,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9952,15 +9989,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9975,7 +10012,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9987,15 +10024,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10010,7 +10047,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10022,15 +10059,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10045,7 +10082,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10063,11 +10100,11 @@
         <v>25</v>
       </c>
       <c t="s" r="K252" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10097,7 +10134,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10109,15 +10146,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10132,7 +10169,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10141,18 +10178,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10167,13 +10204,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>58</v>
@@ -10182,12 +10219,12 @@
         <v>36</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10202,7 +10239,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10214,7 +10251,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>83</v>
@@ -10222,7 +10259,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10237,7 +10274,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10249,15 +10286,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10272,7 +10309,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10284,15 +10321,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10307,7 +10344,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10322,7 +10359,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10355,7 +10392,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10370,12 +10407,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10390,7 +10427,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10405,12 +10442,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10425,7 +10462,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10437,15 +10474,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10460,7 +10497,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10472,15 +10509,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10495,7 +10532,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10507,15 +10544,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>428</v>
+        <v>366</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10545,7 +10582,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10557,7 +10594,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>88</v>
@@ -10565,7 +10602,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10580,7 +10617,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10592,7 +10629,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>90</v>
@@ -10600,7 +10637,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10615,7 +10652,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10624,18 +10661,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10650,27 +10687,27 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
+        <v>151</v>
+      </c>
+      <c t="s" r="H271" s="8">
+        <v>33</v>
+      </c>
+      <c t="s" r="I271" s="7">
+        <v>439</v>
+      </c>
+      <c t="s" r="J271" s="7">
         <v>150</v>
-      </c>
-      <c t="s" r="H271" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I271" s="7">
-        <v>434</v>
-      </c>
-      <c t="s" r="J271" s="7">
-        <v>149</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10685,7 +10722,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10694,18 +10731,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10720,22 +10757,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10768,7 +10805,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10780,15 +10817,15 @@
         <v>93</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10803,7 +10840,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10815,10 +10852,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10838,7 +10875,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10847,18 +10884,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10873,19 +10910,19 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>26</v>
@@ -10893,7 +10930,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10908,7 +10945,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10920,15 +10957,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10943,7 +10980,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10958,7 +10995,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10991,7 +11028,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -11000,13 +11037,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -11026,27 +11063,27 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11061,7 +11098,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11070,18 +11107,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11096,22 +11133,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -11144,7 +11181,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -11153,7 +11190,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>80</v>
@@ -11164,7 +11201,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11179,27 +11216,27 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11214,7 +11251,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -11223,10 +11260,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>26</v>
@@ -11234,7 +11271,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11249,19 +11286,19 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>38</v>
@@ -11269,7 +11306,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11284,7 +11321,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -11293,10 +11330,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>90</v>
@@ -11332,7 +11369,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11344,15 +11381,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11367,7 +11404,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11376,18 +11413,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11417,7 +11454,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11426,18 +11463,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11452,27 +11489,27 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11487,7 +11524,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11496,18 +11533,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11522,27 +11559,27 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11557,7 +11594,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11566,13 +11603,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11592,19 +11629,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>96</v>
@@ -11612,7 +11649,7 @@
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11627,7 +11664,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11636,18 +11673,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11662,22 +11699,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11710,7 +11747,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11725,12 +11762,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11745,7 +11782,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11754,10 +11791,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>91</v>
@@ -11765,7 +11802,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11780,27 +11817,27 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11815,7 +11852,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11824,13 +11861,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I308" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11850,27 +11887,27 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11900,7 +11937,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11912,7 +11949,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>22</v>
@@ -11920,7 +11957,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11935,7 +11972,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11947,15 +11984,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11970,7 +12007,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11982,7 +12019,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>50</v>
@@ -11990,7 +12027,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12005,7 +12042,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12025,7 +12062,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12040,7 +12077,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12049,17 +12086,19 @@
         <v>47</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>477</v>
+        <v>307</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
-      <c r="M315" s="7"/>
+      <c t="s" r="M315" s="7">
+        <v>482</v>
+      </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
       <c t="s" r="A316" s="6">
@@ -12073,22 +12112,22 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -12121,7 +12160,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12133,15 +12172,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12156,7 +12195,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12168,15 +12207,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12191,7 +12230,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12206,12 +12245,12 @@
         <v>37</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12226,7 +12265,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -12238,15 +12277,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12276,7 +12315,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12285,18 +12324,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12311,13 +12350,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>47</v>
@@ -12326,12 +12365,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12346,7 +12385,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12355,10 +12394,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>64</v>
@@ -12366,7 +12405,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12381,27 +12420,27 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12416,7 +12455,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12425,10 +12464,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>110</v>
@@ -12436,7 +12475,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12451,13 +12490,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>47</v>
@@ -12466,12 +12505,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12486,7 +12525,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12495,18 +12534,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12521,13 +12560,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>47</v>
@@ -12536,7 +12575,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -12569,7 +12608,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12584,12 +12623,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12604,7 +12643,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12616,15 +12655,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12639,7 +12678,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12651,15 +12690,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12674,7 +12713,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12683,18 +12722,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12709,13 +12748,13 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>47</v>
@@ -12724,12 +12763,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12744,7 +12783,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12756,10 +12795,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12792,7 +12831,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12807,12 +12846,12 @@
         <v>45</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12827,7 +12866,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12836,10 +12875,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>52</v>
@@ -12847,7 +12886,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12862,19 +12901,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>26</v>
@@ -12882,7 +12921,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12912,7 +12951,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12921,20 +12960,20 @@
         <v>33</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="K343" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12949,13 +12988,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>33</v>
@@ -12969,7 +13008,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12984,7 +13023,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12993,18 +13032,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13019,27 +13058,27 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13054,7 +13093,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13063,10 +13102,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>100</v>
@@ -13074,7 +13113,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13089,19 +13128,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>84</v>
@@ -13109,7 +13148,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13139,7 +13178,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13159,7 +13198,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13174,7 +13213,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13186,15 +13225,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13209,7 +13248,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -13221,7 +13260,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>36</v>
@@ -13229,7 +13268,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13244,7 +13283,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13256,17 +13295,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="K353" s="7">
         <v>91</v>
       </c>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13281,7 +13320,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13293,15 +13332,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13316,7 +13355,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13325,17 +13364,19 @@
         <v>33</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
-      <c r="M355" s="7"/>
+      <c t="s" r="M355" s="7">
+        <v>516</v>
+      </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
       <c t="s" r="A356" s="6">
@@ -13349,22 +13390,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13397,7 +13438,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13406,10 +13447,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>19</v>
@@ -13417,7 +13458,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13432,27 +13473,27 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13467,7 +13508,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13476,18 +13517,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13502,27 +13543,27 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13552,7 +13593,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13561,10 +13602,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>65</v>
@@ -13572,7 +13613,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13587,27 +13628,27 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13622,7 +13663,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13637,12 +13678,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13657,7 +13698,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13669,15 +13710,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13692,7 +13733,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13704,14 +13745,16 @@
         <v>33</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
-      <c r="M367" s="7"/>
+      <c t="s" r="M367" s="7">
+        <v>531</v>
+      </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
       <c r="A368" s="6"/>
@@ -13740,7 +13783,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13752,15 +13795,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13775,7 +13818,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13787,15 +13830,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13806,11 +13849,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C371" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13819,13 +13862,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13839,26 +13882,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C372" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>58</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13891,7 +13934,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13900,18 +13943,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13926,13 +13969,13 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>33</v>
@@ -13941,12 +13984,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13961,7 +14004,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13976,12 +14019,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13996,7 +14039,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14008,7 +14051,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>64</v>
@@ -14016,7 +14059,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14031,7 +14074,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14040,18 +14083,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14066,27 +14109,27 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14101,27 +14144,27 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14136,22 +14179,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -14184,7 +14227,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14196,15 +14239,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14219,7 +14262,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14231,15 +14274,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14254,7 +14297,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14263,18 +14306,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14289,13 +14332,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>47</v>
@@ -14309,7 +14352,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14324,7 +14367,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14336,10 +14379,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14359,7 +14402,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14371,15 +14414,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14394,7 +14437,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14403,13 +14446,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -14427,22 +14470,22 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -14475,7 +14518,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14487,17 +14530,17 @@
         <v>79</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>34</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14512,7 +14555,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14527,12 +14570,12 @@
         <v>94</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14547,7 +14590,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14559,15 +14602,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14582,7 +14625,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14594,7 +14637,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>75</v>
@@ -14602,7 +14645,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14632,7 +14675,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14647,12 +14690,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14667,7 +14710,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14679,15 +14722,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14717,7 +14760,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14729,7 +14772,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>52</v>
@@ -14737,7 +14780,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14752,7 +14795,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14764,15 +14807,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14787,7 +14830,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14796,18 +14839,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14822,22 +14865,22 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14870,7 +14913,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14879,18 +14922,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14905,19 +14948,19 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>108</v>
@@ -14940,7 +14983,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14949,18 +14992,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14975,27 +15018,27 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15025,7 +15068,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -15034,10 +15077,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>49</v>
@@ -15045,7 +15088,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15060,13 +15103,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>63</v>
@@ -15075,12 +15118,12 @@
         <v>50</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15095,7 +15138,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -15104,18 +15147,18 @@
         <v>63</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15130,19 +15173,19 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>104</v>
@@ -15178,7 +15221,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -15187,18 +15230,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15213,13 +15256,13 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>47</v>
@@ -15228,12 +15271,12 @@
         <v>90</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15248,7 +15291,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15268,7 +15311,7 @@
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15283,7 +15326,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -15295,15 +15338,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15333,7 +15376,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -15345,15 +15388,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15368,7 +15411,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -15377,18 +15420,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15403,13 +15446,13 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>17</v>
@@ -15418,7 +15461,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -15451,27 +15494,27 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15486,13 +15529,13 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>33</v>
@@ -15501,12 +15544,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15521,7 +15564,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -15530,18 +15573,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15567,31 +15610,31 @@
         <v>1615</v>
       </c>
       <c t="s" r="C428" s="7">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15606,7 +15649,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -15621,12 +15664,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15641,7 +15684,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15653,7 +15696,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>108</v>
@@ -15691,13 +15734,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>33</v>
@@ -15706,12 +15749,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15726,7 +15769,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
@@ -15738,15 +15781,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15761,7 +15804,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -15773,10 +15816,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15811,7 +15854,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -15823,7 +15866,7 @@
         <v>58</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>56</v>
@@ -15831,7 +15874,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15846,7 +15889,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15855,18 +15898,18 @@
         <v>58</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15881,22 +15924,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15929,7 +15972,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15938,18 +15981,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15964,27 +16007,27 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15999,27 +16042,27 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16049,7 +16092,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -16058,18 +16101,18 @@
         <v>33</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16084,32 +16127,32 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c t="s" r="A446" s="9">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B446" s="9"/>
       <c r="C446" s="9"/>
@@ -16129,7 +16172,7 @@
     <row r="447" ht="65.25" customHeight="1"/>
     <row r="448" ht="16.5" customHeight="1">
       <c t="s" r="A448" s="10">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="B448" s="10"/>
       <c r="C448" s="10"/>
@@ -16142,7 +16185,7 @@
       <c r="J448" s="10"/>
       <c r="K448" s="10"/>
       <c t="s" r="L448" s="11">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="M448" s="11"/>
       <c r="N448" s="11"/>
